--- a/01_Ejercicios prácticos/20251104_ejercicio_17/1_syuzhet/1_syuzhet_resultados.xlsx
+++ b/01_Ejercicios prácticos/20251104_ejercicio_17/1_syuzhet/1_syuzhet_resultados.xlsx
@@ -1,23 +1,329 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorgejuvenalcamposferreira/Documents/GitHub/TC2002B.651-Ciencia-de-datos/01_Ejercicios prácticos/20251104_ejercicio_17/1_syuzhet/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40C7102-9BD5-6644-9578-8424E9ED621A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="100" yWindow="760" windowWidth="24980" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="resultados" sheetId="1" r:id="rId1"/>
     <sheet name="accuracy" sheetId="2" r:id="rId2"/>
     <sheet name="matriz_confusion" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="94">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>contexto</t>
+  </si>
+  <si>
+    <t>texto</t>
+  </si>
+  <si>
+    <t>etiqueta_real</t>
+  </si>
+  <si>
+    <t>tipo_caso</t>
+  </si>
+  <si>
+    <t>notas</t>
+  </si>
+  <si>
+    <t>syuzhet_score</t>
+  </si>
+  <si>
+    <t>pred_syuzhet</t>
+  </si>
+  <si>
+    <t>anger</t>
+  </si>
+  <si>
+    <t>anticipation</t>
+  </si>
+  <si>
+    <t>disgust</t>
+  </si>
+  <si>
+    <t>fear</t>
+  </si>
+  <si>
+    <t>joy</t>
+  </si>
+  <si>
+    <t>sadness</t>
+  </si>
+  <si>
+    <t>surprise</t>
+  </si>
+  <si>
+    <t>trust</t>
+  </si>
+  <si>
+    <t>negative</t>
+  </si>
+  <si>
+    <t>positive</t>
+  </si>
+  <si>
+    <t>Restaurante</t>
+  </si>
+  <si>
+    <t>La comida estuvo deliciosa, el servicio excelente y el ambiente perfecto. Totalmente recomendado.</t>
+  </si>
+  <si>
+    <t>positivo</t>
+  </si>
+  <si>
+    <t>claro_positivo</t>
+  </si>
+  <si>
+    <t>neutro</t>
+  </si>
+  <si>
+    <t>Increíble experiencia culinaria. Los platillos superaron mis expectativas. Volveré sin duda.</t>
+  </si>
+  <si>
+    <t>negativo</t>
+  </si>
+  <si>
+    <t>Excelente atención del personal y la comida llegó rápido y caliente. Muy satisfecho.</t>
+  </si>
+  <si>
+    <t>Me encantó todo, desde la entrada hasta el postre. Precios justos y gran calidad.</t>
+  </si>
+  <si>
+    <t>¡Wow! El mejor restaurante al que he ido en mucho tiempo. Todo perfecto.</t>
+  </si>
+  <si>
+    <t>Pésimo servicio, la comida llegó fría y el mesero fue grosero. No vuelvo más.</t>
+  </si>
+  <si>
+    <t>claro_negativo</t>
+  </si>
+  <si>
+    <t>Una hora esperando y cuando llegó la comida estaba horrible. Muy decepcionado.</t>
+  </si>
+  <si>
+    <t>Carísimo para lo que ofrecen. La comida es mediocre y el lugar estaba sucio.</t>
+  </si>
+  <si>
+    <t>La peor experiencia gastronómica de mi vida. No lo recomiendo para nada.</t>
+  </si>
+  <si>
+    <t>El personal parecía molesto por atendernos. La comida sin sabor y cara.</t>
+  </si>
+  <si>
+    <t>Un restaurante normal. La comida está bien, nada extraordinario pero cumple.</t>
+  </si>
+  <si>
+    <t>claro_neutro</t>
+  </si>
+  <si>
+    <t>Es un lugar promedio. Ni bueno ni malo, sirve para salir del paso.</t>
+  </si>
+  <si>
+    <t>Genial, justo lo que quería: esperar dos horas para comer algo frío.</t>
+  </si>
+  <si>
+    <t>sarcasmo</t>
+  </si>
+  <si>
+    <t>Qué maravilla de restaurante, me encanta pagar mucho por comida mala.</t>
+  </si>
+  <si>
+    <t>La comida está rica pero el servicio es lentísimo y los precios muy altos.</t>
+  </si>
+  <si>
+    <t>mixto</t>
+  </si>
+  <si>
+    <t>Producto Tech</t>
+  </si>
+  <si>
+    <t>Excelente producto, funciona perfecto y llegó antes de tiempo. Muy recomendable.</t>
+  </si>
+  <si>
+    <t>La mejor compra que he hecho. Calidad increíble y precio justo.</t>
+  </si>
+  <si>
+    <t>Superó mis expectativas por completo. Funciona de maravilla y es muy intuitivo.</t>
+  </si>
+  <si>
+    <t>100% satisfecho con mi compra. Llevo un mes usándolo sin problemas.</t>
+  </si>
+  <si>
+    <t>Producto de alta calidad. Vale cada peso. Lo recomiendo ampliamente.</t>
+  </si>
+  <si>
+    <t>No funciona como prometen. Me arrepiento de la compra, es una estafa.</t>
+  </si>
+  <si>
+    <t>Pésima calidad, se descompuso a la semana. No lo compren.</t>
+  </si>
+  <si>
+    <t>Horrible producto. No sirve para nada y el soporte técnico es inexistente.</t>
+  </si>
+  <si>
+    <t>Basura total. No cumple con ninguna de las especificaciones anunciadas.</t>
+  </si>
+  <si>
+    <t>Me llegó defectuoso y nadie responde para hacer la devolución. Fatal.</t>
+  </si>
+  <si>
+    <t>Es un producto básico que cumple su función. Nada especial pero funciona.</t>
+  </si>
+  <si>
+    <t>Ni bueno ni malo. Hace lo que tiene que hacer, sin más.</t>
+  </si>
+  <si>
+    <t>Perfecto, me encanta cuando los productos no funcionan al sacarlos de la caja.</t>
+  </si>
+  <si>
+    <t>Fantástico, justo necesitaba algo que se rompiera en una semana.</t>
+  </si>
+  <si>
+    <t>El producto es bueno pero llegó tarde y el empaque venía dañado.</t>
+  </si>
+  <si>
+    <t>Servicio</t>
+  </si>
+  <si>
+    <t>Servicio impecable. Muy profesionales y resolvieron mi problema rápidamente.</t>
+  </si>
+  <si>
+    <t>Excelente atención al cliente. Me ayudaron en todo momento. Muy agradecido.</t>
+  </si>
+  <si>
+    <t>Súper eficientes y amables. El mejor servicio que he recibido.</t>
+  </si>
+  <si>
+    <t>Quedé muy satisfecho con el trabajo realizado. Altamente recomendable.</t>
+  </si>
+  <si>
+    <t>Profesionales de primera. Cumplieron todo lo prometido y más.</t>
+  </si>
+  <si>
+    <t>Pésimo servicio. No resolvieron nada y además fueron groseros.</t>
+  </si>
+  <si>
+    <t>Nunca contestaron mis llamadas. Servicio al cliente inexistente. Terrible.</t>
+  </si>
+  <si>
+    <t>Me cobraron de más y cuando reclamé me colgaron el teléfono. Indignante.</t>
+  </si>
+  <si>
+    <t>El peor servicio que he contratado. Llegaron tarde y el trabajo quedó mal.</t>
+  </si>
+  <si>
+    <t>No lo recomiendo. Son poco profesionales y el servicio es malísimo.</t>
+  </si>
+  <si>
+    <t>Servicio regular. Cumplieron pero sin nada destacable.</t>
+  </si>
+  <si>
+    <t>Normal. Hicieron lo básico que pedí, nada más.</t>
+  </si>
+  <si>
+    <t>Increíble servicio, me encanta que me dejen esperando tres horas sin avisar.</t>
+  </si>
+  <si>
+    <t>Qué atención tan maravillosa, ignorar a los clientes es su especialidad.</t>
+  </si>
+  <si>
+    <t>El trabajo quedó bien pero tardaron el doble de lo acordado.</t>
+  </si>
+  <si>
+    <t>App/Software</t>
+  </si>
+  <si>
+    <t>App excelente, muy intuitiva y rápida. La uso todos los días.</t>
+  </si>
+  <si>
+    <t>La mejor aplicación en su categoría. Funciona perfecto y sin bugs.</t>
+  </si>
+  <si>
+    <t>Me encanta esta app. Interface limpia y cumple perfectamente su función.</t>
+  </si>
+  <si>
+    <t>Súper útil y bien diseñada. Vale la pena la versión premium.</t>
+  </si>
+  <si>
+    <t>Aplicación fantástica. Ha mejorado mucho mi productividad.</t>
+  </si>
+  <si>
+    <t>App horrible. Se cuelga constantemente y pierde mi información.</t>
+  </si>
+  <si>
+    <t>No sirve. Llena de anuncios y funciona muy mal. La desinstalé.</t>
+  </si>
+  <si>
+    <t>Pésima experiencia. Crashea todo el tiempo y consume mucha batería.</t>
+  </si>
+  <si>
+    <t>Basura de aplicación. No funciona ni la mitad de las funciones.</t>
+  </si>
+  <si>
+    <t>La peor app que he usado. Interface confusa y llena de errores.</t>
+  </si>
+  <si>
+    <t>App normal. Hace lo básico pero nada impresionante.</t>
+  </si>
+  <si>
+    <t>Está bien para uso ocasional. Ni buena ni mala.</t>
+  </si>
+  <si>
+    <t>Genial, me fascina cuando una app se cierra sola cada cinco minutos.</t>
+  </si>
+  <si>
+    <t>Perfecta, justo lo que buscaba: pagar por una app que no funciona.</t>
+  </si>
+  <si>
+    <t>La app tiene buenas funciones pero es muy lenta y tiene muchos anuncios.</t>
+  </si>
+  <si>
+    <t>accuracy</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>correctos</t>
+  </si>
+  <si>
+    <t>Igual</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,13 +371,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -109,7 +423,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -143,6 +457,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -177,9 +492,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -352,133 +668,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="19" max="19" width="15.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>contexto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>etiqueta_real</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tipo_caso</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>notas</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>syuzhet_score</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>pred_syuzhet</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>anger</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>anticipation</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>disgust</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>joy</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>sadness</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>surprise</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>La comida estuvo deliciosa, el servicio excelente y el ambiente perfecto. Totalmente recomendado.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H2" t="s">
+        <v>22</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -510,38 +786,32 @@
       <c r="R2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="S2" t="b">
+        <f>EXACT(H2,D2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Increíble experiencia culinaria. Los platillos superaron mis expectativas. Volveré sin duda.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
       </c>
       <c r="G3">
         <v>-0.75</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H3" t="s">
+        <v>24</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -573,38 +843,32 @@
       <c r="R3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="S3" t="b">
+        <f t="shared" ref="S3:S61" si="0">EXACT(H3,D3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Excelente atención del personal y la comida llegó rápido y caliente. Muy satisfecho.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H4" t="s">
+        <v>22</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -636,38 +900,32 @@
       <c r="R4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="S4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Me encantó todo, desde la entrada hasta el postre. Precios justos y gran calidad.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H5" t="s">
+        <v>22</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -699,38 +957,32 @@
       <c r="R5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="S5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>¡Wow! El mejor restaurante al que he ido en mucho tiempo. Todo perfecto.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
       </c>
       <c r="G6">
         <v>0.5</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
+      <c r="H6" t="s">
+        <v>20</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -762,38 +1014,32 @@
       <c r="R6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="S6" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pésimo servicio, la comida llegó fría y el mesero fue grosero. No vuelvo más.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H7" t="s">
+        <v>22</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -825,38 +1071,32 @@
       <c r="R7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="S7" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Una hora esperando y cuando llegó la comida estaba horrible. Muy decepcionado.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
       </c>
       <c r="G8">
         <v>-0.75</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H8" t="s">
+        <v>24</v>
       </c>
       <c r="I8">
         <v>4</v>
@@ -888,38 +1128,32 @@
       <c r="R8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="S8" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Carísimo para lo que ofrecen. La comida es mediocre y el lugar estaba sucio.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
       </c>
       <c r="G9">
         <v>-0.75</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H9" t="s">
+        <v>24</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -951,38 +1185,32 @@
       <c r="R9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="S9" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>La peor experiencia gastronómica de mi vida. No lo recomiendo para nada.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H10" t="s">
+        <v>22</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1014,38 +1242,32 @@
       <c r="R10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="S10" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>El personal parecía molesto por atendernos. La comida sin sabor y cara.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
       </c>
       <c r="G11">
         <v>-0.75</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H11" t="s">
+        <v>24</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -1077,38 +1299,32 @@
       <c r="R11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="S11" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Un restaurante normal. La comida está bien, nada extraordinario pero cumple.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>claro_neutro</t>
-        </is>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H12" t="s">
+        <v>22</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1140,38 +1356,32 @@
       <c r="R12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="S12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Es un lugar promedio. Ni bueno ni malo, sirve para salir del paso.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>claro_neutro</t>
-        </is>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H13" t="s">
+        <v>22</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -1203,38 +1413,32 @@
       <c r="R13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="S13" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Genial, justo lo que quería: esperar dos horas para comer algo frío.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>sarcasmo</t>
-        </is>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
       </c>
       <c r="G14">
         <v>0.75</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
+      <c r="H14" t="s">
+        <v>20</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1266,38 +1470,32 @@
       <c r="R14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="S14" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Qué maravilla de restaurante, me encanta pagar mucho por comida mala.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>sarcasmo</t>
-        </is>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H15" t="s">
+        <v>22</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -1329,38 +1527,32 @@
       <c r="R15">
         <v>4</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="S15" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>La comida está rica pero el servicio es lentísimo y los precios muy altos.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>mixto</t>
-        </is>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H16" t="s">
+        <v>22</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1392,38 +1584,32 @@
       <c r="R16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="S16" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Excelente producto, funciona perfecto y llegó antes de tiempo. Muy recomendable.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H17" t="s">
+        <v>22</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1455,38 +1641,32 @@
       <c r="R17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="S17" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>La mejor compra que he hecho. Calidad increíble y precio justo.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H18" t="s">
+        <v>22</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1518,38 +1698,32 @@
       <c r="R18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19">
+      <c r="S18" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Superó mis expectativas por completo. Funciona de maravilla y es muy intuitivo.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
       </c>
       <c r="G19">
         <v>0.75</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
+      <c r="H19" t="s">
+        <v>20</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1581,38 +1755,32 @@
       <c r="R19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="S19" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>100% satisfecho con mi compra. Llevo un mes usándolo sin problemas.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
       </c>
       <c r="G20">
         <v>-1</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H20" t="s">
+        <v>24</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1644,38 +1812,32 @@
       <c r="R20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="S20" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Producto de alta calidad. Vale cada peso. Lo recomiendo ampliamente.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H21" t="s">
+        <v>22</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1707,38 +1869,32 @@
       <c r="R21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="S21" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No funciona como prometen. Me arrepiento de la compra, es una estafa.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H22" t="s">
+        <v>22</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1770,38 +1926,32 @@
       <c r="R22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="S22" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Pésima calidad, se descompuso a la semana. No lo compren.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H23" t="s">
+        <v>22</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1833,38 +1983,32 @@
       <c r="R23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="S23" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Horrible producto. No sirve para nada y el soporte técnico es inexistente.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
       </c>
       <c r="G24">
         <v>-0.75</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H24" t="s">
+        <v>24</v>
       </c>
       <c r="I24">
         <v>3</v>
@@ -1896,38 +2040,32 @@
       <c r="R24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25">
+      <c r="S24" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Basura total. No cumple con ninguna de las especificaciones anunciadas.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
       </c>
       <c r="G25">
         <v>-0.25</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H25" t="s">
+        <v>24</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1959,38 +2097,32 @@
       <c r="R25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="S25" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Me llegó defectuoso y nadie responde para hacer la devolución. Fatal.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
       </c>
       <c r="G26">
         <v>-0.5</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H26" t="s">
+        <v>24</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -2022,38 +2154,32 @@
       <c r="R26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27">
+      <c r="S26" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Es un producto básico que cumple su función. Nada especial pero funciona.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>claro_neutro</t>
-        </is>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
+        <v>35</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H27" t="s">
+        <v>22</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2085,38 +2211,32 @@
       <c r="R27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28">
+      <c r="S27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ni bueno ni malo. Hace lo que tiene que hacer, sin más.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>claro_neutro</t>
-        </is>
+      <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
+        <v>35</v>
       </c>
       <c r="G28">
         <v>-0.75</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H28" t="s">
+        <v>24</v>
       </c>
       <c r="I28">
         <v>1</v>
@@ -2148,38 +2268,32 @@
       <c r="R28">
         <v>4</v>
       </c>
-    </row>
-    <row r="29">
+      <c r="S28" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Perfecto, me encanta cuando los productos no funcionan al sacarlos de la caja.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>sarcasmo</t>
-        </is>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>38</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H29" t="s">
+        <v>22</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2211,38 +2325,32 @@
       <c r="R29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30">
+      <c r="S29" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Fantástico, justo necesitaba algo que se rompiera en una semana.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>sarcasmo</t>
-        </is>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
+        <v>38</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H30" t="s">
+        <v>22</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2274,38 +2382,32 @@
       <c r="R30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="S30" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Producto Tech</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>El producto es bueno pero llegó tarde y el empaque venía dañado.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>mixto</t>
-        </is>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" t="s">
+        <v>41</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H31" t="s">
+        <v>22</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2337,38 +2439,32 @@
       <c r="R31">
         <v>3</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="S31" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Servicio impecable. Muy profesionales y resolvieron mi problema rápidamente.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>21</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H32" t="s">
+        <v>22</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2400,38 +2496,32 @@
       <c r="R32">
         <v>2</v>
       </c>
-    </row>
-    <row r="33">
+      <c r="S32" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Excelente atención al cliente. Me ayudaron en todo momento. Muy agradecido.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H33" t="s">
+        <v>22</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2463,38 +2553,32 @@
       <c r="R33">
         <v>4</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="S33" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Súper eficientes y amables. El mejor servicio que he recibido.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H34" t="s">
+        <v>22</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2526,38 +2610,32 @@
       <c r="R34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="S34" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Quedé muy satisfecho con el trabajo realizado. Altamente recomendable.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
       </c>
       <c r="G35">
         <v>-0.25</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H35" t="s">
+        <v>24</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2589,38 +2667,32 @@
       <c r="R35">
         <v>6</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="S35" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Profesionales de primera. Cumplieron todo lo prometido y más.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>21</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H36" t="s">
+        <v>22</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2652,38 +2724,32 @@
       <c r="R36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="S36" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Pésimo servicio. No resolvieron nada y además fueron groseros.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H37" t="s">
+        <v>22</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2715,38 +2781,32 @@
       <c r="R37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="S37" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Nunca contestaron mis llamadas. Servicio al cliente inexistente. Terrible.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" t="s">
+        <v>29</v>
       </c>
       <c r="G38">
         <v>-0.75</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H38" t="s">
+        <v>24</v>
       </c>
       <c r="I38">
         <v>2</v>
@@ -2778,38 +2838,32 @@
       <c r="R38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39">
+      <c r="S38" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Me cobraron de más y cuando reclamé me colgaron el teléfono. Indignante.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H39" t="s">
+        <v>22</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2841,38 +2895,32 @@
       <c r="R39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40">
+      <c r="S39" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>El peor servicio que he contratado. Llegaron tarde y el trabajo quedó mal.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H40" t="s">
+        <v>22</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -2904,38 +2952,32 @@
       <c r="R40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="S40" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No lo recomiendo. Son poco profesionales y el servicio es malísimo.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H41" t="s">
+        <v>22</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -2967,38 +3009,32 @@
       <c r="R41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42">
+      <c r="S41" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Servicio regular. Cumplieron pero sin nada destacable.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>claro_neutro</t>
-        </is>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" t="s">
+        <v>35</v>
       </c>
       <c r="G42">
         <v>-0.75</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H42" t="s">
+        <v>24</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3030,38 +3066,32 @@
       <c r="R42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43">
+      <c r="S42" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Normal. Hicieron lo básico que pedí, nada más.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>claro_neutro</t>
-        </is>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" t="s">
+        <v>35</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H43" t="s">
+        <v>22</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -3093,38 +3123,32 @@
       <c r="R43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="S43" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Increíble servicio, me encanta que me dejen esperando tres horas sin avisar.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>sarcasmo</t>
-        </is>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="s">
+        <v>71</v>
+      </c>
+      <c r="D44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" t="s">
+        <v>38</v>
       </c>
       <c r="G44">
         <v>-0.75</v>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H44" t="s">
+        <v>24</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3156,38 +3180,32 @@
       <c r="R44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="S44" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Qué atención tan maravillosa, ignorar a los clientes es su especialidad.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>sarcasmo</t>
-        </is>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" t="s">
+        <v>38</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H45" t="s">
+        <v>22</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3219,38 +3237,32 @@
       <c r="R45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46">
+      <c r="S45" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>El trabajo quedó bien pero tardaron el doble de lo acordado.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>mixto</t>
-        </is>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" t="s">
+        <v>41</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H46" t="s">
+        <v>22</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3282,38 +3294,32 @@
       <c r="R46">
         <v>2</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="S46" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>App excelente, muy intuitiva y rápida. La uso todos los días.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B47" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
+        <v>21</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H47" t="s">
+        <v>22</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3345,38 +3351,32 @@
       <c r="R47">
         <v>2</v>
       </c>
-    </row>
-    <row r="48">
+      <c r="S47" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>La mejor aplicación en su categoría. Funciona perfecto y sin bugs.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B48" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
+        <v>21</v>
       </c>
       <c r="G48">
         <v>-0.75</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H48" t="s">
+        <v>24</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3408,38 +3408,32 @@
       <c r="R48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49">
+      <c r="S48" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Me encanta esta app. Interface limpia y cumple perfectamente su función.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B49" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" t="s">
+        <v>21</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H49" t="s">
+        <v>22</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3471,38 +3465,32 @@
       <c r="R49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="S49" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Súper útil y bien diseñada. Vale la pena la versión premium.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B50" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
+        <v>21</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H50" t="s">
+        <v>22</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -3534,38 +3522,32 @@
       <c r="R50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51">
+      <c r="S50" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Aplicación fantástica. Ha mejorado mucho mi productividad.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>claro_positivo</t>
-        </is>
+      <c r="B51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>21</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H51" t="s">
+        <v>22</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -3597,38 +3579,32 @@
       <c r="R51">
         <v>2</v>
       </c>
-    </row>
-    <row r="52">
+      <c r="S51" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>App horrible. Se cuelga constantemente y pierde mi información.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
       </c>
       <c r="G52">
         <v>-0.75</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+      <c r="H52" t="s">
+        <v>24</v>
       </c>
       <c r="I52">
         <v>3</v>
@@ -3660,38 +3636,32 @@
       <c r="R52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53">
+      <c r="S52" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>No sirve. Llena de anuncios y funciona muy mal. La desinstalé.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H53" t="s">
+        <v>22</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -3723,38 +3693,32 @@
       <c r="R53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54">
+      <c r="S53" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Pésima experiencia. Crashea todo el tiempo y consume mucha batería.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B54" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" t="s">
+        <v>29</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H54" t="s">
+        <v>22</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3786,38 +3750,32 @@
       <c r="R54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55">
+      <c r="S54" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Basura de aplicación. No funciona ni la mitad de las funciones.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B55" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H55" t="s">
+        <v>22</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3849,38 +3807,32 @@
       <c r="R55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56">
+      <c r="S55" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>La peor app que he usado. Interface confusa y llena de errores.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>claro_negativo</t>
-        </is>
+      <c r="B56" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" t="s">
+        <v>29</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H56" t="s">
+        <v>22</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3912,38 +3864,32 @@
       <c r="R56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57">
+      <c r="S56" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>App normal. Hace lo básico pero nada impresionante.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>claro_neutro</t>
-        </is>
+      <c r="B57" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" t="s">
+        <v>35</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H57" t="s">
+        <v>22</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3975,38 +3921,32 @@
       <c r="R57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58">
+      <c r="S57" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Está bien para uso ocasional. Ni buena ni mala.</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>claro_neutro</t>
-        </is>
+      <c r="B58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" t="s">
+        <v>35</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H58" t="s">
+        <v>22</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -4038,38 +3978,32 @@
       <c r="R58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59">
+      <c r="S58" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Genial, me fascina cuando una app se cierra sola cada cinco minutos.</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>sarcasmo</t>
-        </is>
+      <c r="B59" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" t="s">
+        <v>87</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" t="s">
+        <v>38</v>
       </c>
       <c r="G59">
         <v>0.75</v>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
+      <c r="H59" t="s">
+        <v>20</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -4101,38 +4035,32 @@
       <c r="R59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60">
+      <c r="S59" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Perfecta, justo lo que buscaba: pagar por una app que no funciona.</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>sarcasmo</t>
-        </is>
+      <c r="B60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" t="s">
+        <v>88</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" t="s">
+        <v>38</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H60" t="s">
+        <v>22</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -4164,38 +4092,32 @@
       <c r="R60">
         <v>3</v>
       </c>
-    </row>
-    <row r="61">
+      <c r="S60" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>App/Software</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>La app tiene buenas funciones pero es muy lenta y tiene muchos anuncios.</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>mixto</t>
-        </is>
+      <c r="B61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" t="s">
+        <v>41</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+      <c r="H61" t="s">
+        <v>22</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -4225,6 +4147,10 @@
         <v>1</v>
       </c>
       <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61" t="b">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4234,30 +4160,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>correctos</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>0.3166666666666667</v>
+        <v>0.31666666666666671</v>
       </c>
       <c r="B2">
         <v>60</v>
@@ -4272,37 +4192,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>etiqueta_real</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>24</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -4314,11 +4224,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>neutro</t>
-        </is>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>22</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -4330,11 +4238,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>20</v>
       </c>
       <c r="B4">
         <v>4</v>
